--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_05_Full_78_Cau/Day_05_Ngan_Hang_Phan_01_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_05_Full_78_Cau/Day_05_Ngan_Hang_Phan_01_20_Cau.xlsx
@@ -1238,7 +1238,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Thử nghiệm phải tạo bằng chứng trước khi đầu tư tự động hóa.</t>
+          <t>Các thành phần bắt buộc của thử nghiệm Wizard-of-Oz: Người sáng lập tạo biên bản thủ công phía sau giao diện (a), Ghi rõ quy trình thủ công và giới hạn của bằng chứng (b), Đo lường mức độ người dùng sử dụng/sẵn sàng trả tiền và chất lượng biên bản (c), và Đặt trước tiêu chí tiếp tục hoặc dừng thử nghiệm (e).</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Khía cạnh cần kiểm phải nối trực tiếp với lý do người dùng chưa đạt kết quả mong muốn.</t>
+          <t>Khi HR không hiểu vì sao ứng viên bị xếp thấp và không dám dùng kết quả, khía cạnh cần kiểm tra và cải thiện trước tiên là Mức độ tin cậy/khả năng giải thích (explainability) và Khả năng sử dụng (usability) của quyết định xếp hạng.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_05_Full_78_Cau/Day_05_Ngan_Hang_Phan_01_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_05_Full_78_Cau/Day_05_Ngan_Hang_Phan_01_20_Cau.xlsx
@@ -675,10 +675,24 @@
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách dấu hiệu làm giá sai khỏi dấu hiệu chỉ làm cách diễn đạt thay đổi.
-Phân tích theo nguyên lý thiết kế: Tách dấu hiệu làm giá sai khỏi dấu hiệu chỉ làm cách diễn đạt thay đổi.</t>
+- 1.0 điểm: Phân loại đúng lớp bất định ngữ cảnh/retrieval kèm bằng chứng bảng giá đã hết hạn.
+- 1.0 điểm: Phân loại đúng lớp bất định đầu vào mơ hồ kèm bằng chứng người dùng chỉ nói 'cuối tuần'.
+- 1.0 điểm: Phân loại đúng tính ngẫu nhiên của mô hình kèm bằng chứng câu chữ khác nhau nhưng cùng số sai.
+- 1.0 điểm: Tách bạch rõ ràng nguyên nhân gây sai số (retrieval) và nguyên nhân gây đổi câu từ (temperature).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân loại các lớp bất định và bằng chứng cụ thể:
+- Lớp bất định dữ liệu ngữ cảnh / Retrieval (Context Data Uncertainty / Epistemic Staleness):
+  + Bằng chứng: Bộ phận retrieval truy xuất bảng giá đã hết hạn từ cơ sở dữ liệu. Đây là nguyên nhân gốc rễ gây ra con số sai, thuộc về tính lỗi thời của tri thức bên ngoài chứ không phải do mô hình tính toán sai.
+- Lớp bất định nhập nhằng đầu vào từ người dùng (Input Ambiguity):
+  + Bằng chứng: Người dùng chỉ nhập cụm từ mơ hồ 'cuối tuần' mà không nói rõ thứ Bảy, Chủ Nhật, hay ngày cụ thể nào, dẫn đến việc hệ thống tra cứu không có bộ lọc thời gian chính xác.
+- Lớp bất định phát sinh của mô hình (Model Stochastic Uncertainty / Aleatoric Variability):
+  + Bằng chứng: Mô hình tạo ra hai phản hồi có câu chữ diễn đạt khác nhau trong hai lần chạy (do sampling temperature &gt; 0), nhưng vẫn giữ nguyên con số sai vì cả hai lần đều cùng dựa trên dữ liệu ngữ cảnh hết hạn từ retrieval.
+2. Kết luận phân định:
+Cần tách bạch rõ ràng: Việc đưa ra con số sai là do lỗi dữ liệu ngữ cảnh lỗi thời (Retrieval Failure), còn việc câu chữ thay đổi chỉ là tính ngẫu nhiên bề mặt trong cách hành văn của LLM.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong sản phẩm AI, việc phân tách các tầng bất định (Uncertainty Layers) giữa Input Ambiguity (đầu vào mơ hồ), Retrieval Inaccuracy (dữ liệu bối cảnh sai lệch) và Model Stochasticity (tính ngẫu nhiên trong diễn đạt) là bước tiên quyết để chẩn đoán lỗi. Nếu nhầm lẫn giữa sự biến thiên câu chữ và lỗi giá sai, đội ngũ kỹ thuật sẽ sửa nhầm prompt thay vì cập nhật cơ chế kiểm tra độ mới của RAG.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google PAIR Guidebook - Designing for AI Uncertainty &amp; System Diagnosis Patterns (https://pair.withgoogle.com/guidebook/)</t>
         </is>
       </c>
     </row>
@@ -762,10 +776,22 @@
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Một thay đổi trong phân bố không tự động chứng minh quan hệ nhân quả.
-Phân tích theo nguyên lý thiết kế: Một thay đổi trong phân bố không tự động chứng minh quan hệ nhân quả.</t>
+- 1.0 điểm: Chẩn đoán chính xác hiện tượng dịch chuyển phân phối dữ liệu đầu vào (Covariate Shift / Data Drift).
+- 1.0 điểm: Nêu rõ bằng chứng về sự thay đổi cơ cấu người dùng (teen tăng từ 5% lên 42%) mà hệ thống chưa kịp thích ứng.
+- 1.0 điểm: Nêu đầy đủ các bằng chứng còn thiếu (đo lỗi phân tầng, danh mục từ lóng mới).
+- 1.0 điểm: Nêu dứt khoát điều chưa được phép kết luận (không được kết luận model bị thoái hóa hay prompt bị lỗi).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Chẩn đoán chính (Primary Diagnosis):
+Hiện tượng dịch chuyển phân phối dữ liệu đầu vào thực tế (Data Drift / Covariate Shift). Hệ thống không hề bị lỗi mã nguồn hay suy giảm mô hình, mà đối tượng người dùng thực tế đã thay đổi cấu trúc: tỷ lệ truy vấn của nhóm tuổi teen (nhóm có mật độ sử dụng từ lóng rất cao) tăng đột biến từ 5% lên 42%. Bộ từ vựng và ngữ cảnh huấn luyện/prompt ban đầu không được tối ưu cho phân phối ngôn ngữ mới này.
+2. Bằng chứng còn cần bổ sung để xác thực quan hệ nhân quả:
+- Phân tích phân tầng tỷ lệ lỗi (Stratified Error Rate): Cần đo lường tỷ lệ hiểu sai từ lóng riêng biệt trên hai tập: nhóm teen và nhóm người dùng truyền thống. Nếu tỷ lệ lỗi ở nhóm teen cao vượt trội và nhóm truyền thống vẫn ổn định, chẩn đoán Covariate Shift được chứng minh.
+- Bộ mẫu từ lóng mới xuất hiện: Trích xuất danh sách các từ lóng xuất hiện trong các câu truy vấn thất bại để kiểm tra xem đó là tiếng lóng thế hệ mới (ngoài tri thức của LLM) hay do lỗi trích xuất ý định.
+3. Điều TUYỆT ĐỐI CHƯA ĐƯỢC PHÉP KẾT LUẬN:
+Chưa được phép kết luận rằng 'Năng lực mô hình cơ sở bị giảm sút' (Model Degradation) hoặc 'Hệ thống bị lỗi prompt/kho tri thức', vì phiên bản model, prompt hash và knowledge base snapshot đều được giữ nguyên 100%.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Sự suy giảm hiệu năng của sản phẩm AI sau khi phát hành thường bắt nguồn từ Data Drift hơn là Model Drift. Một sự thay đổi về tỷ lệ nhân khẩu học (từ 5% lên 42% teen) là một tương quan mạnh mẽ, nhưng PM/Kỹ sư cần bằng chứng phân tầng trước khi vội vàng đổ lỗi cho mô hình nền tảng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Chip Huyen - Designing Machine Learning Systems (Chapter 8: Data Distribution Shifts and Monitoring) (https://huyenchip.com/machine-learning-systems-design/)</t>
         </is>
       </c>
     </row>
@@ -850,10 +876,28 @@
       <c r="K8" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Mỗi thay đổi phải trả lời rõ: ai sửa gì, ở đâu và kiểm lại bằng bằng chứng nào.
-Phân tích theo nguyên lý thiết kế: Mỗi thay đổi phải trả lời rõ: ai sửa gì, ở đâu và kiểm lại bằng bằng chứng nào.</t>
+- 1.0 điểm: Thay đổi 1 (Yêu cầu/Phạm vi) đầy đủ nội dung, phân công rõ Product Manager và tài liệu PRD/Scope Matrix.
+- 1.0 điểm: Thay đổi 2 (UX khôi phục) đầy đủ nội dung thông báo có tính xây dựng, phân công UX Designer và bản thiết kế Figma.
+- 1.0 điểm: Thay đổi 3 (Kiểm chứng) đầy đủ bộ test case out-of-scope, phân công QA/Eval Engineer và Test Suite report.
+- 1.0 điểm: Giải quyết triệt để lỗi người dùng nhìn thấy ('đã có lỗi' thành graceful recovery).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Chuyển đổi sự cố thành ba thay đổi cụ thể kèm người phụ trách và tài liệu đầu ra:
+1. Thay đổi về Yêu cầu / Phạm vi (Scope &amp; Requirements Change):
+- Nội dung thay đổi: Bổ sung rõ ràng ranh giới phạm vi phục vụ (Scope Boundary) của bot. Định nghĩa rõ các ý định ngoài phạm vi (Out-of-Scope Intents), ví dụ 'đặt vé máy bay', 'đặt vé tàu', 'thuê xe', và quy định bot phải từ chối lịch sự kèm chỉ dẫn thay vì báo lỗi hệ thống chung chung.
+- Người phụ trách: Product Manager (AI PM).
+- Tài liệu đầu ra: Cập nhật Bản đặc tả yêu cầu sản phẩm (PRD - Out-of-Scope Handling Matrix) &amp; Danh mục phân loại Intent Boundary.
+2. Thay đổi về Trải nghiệm khôi phục lỗi (UX Recovery Change):
+- Nội dung thay đổi: Thay thế thông báo chết 'Đã có lỗi' bằng giao diện thông báo ranh giới có tính xây dựng (Graceful Fallback UX): 'Hiện tại mình chỉ hỗ trợ đặt vé xem phim/sự kiện, chưa hỗ trợ vé tàu. Bạn có muốn tra cứu vé xem phim hay cần mình kết nối tới tổng đài hỗ trợ đối tác không?' kèm các nút gợi ý thao tác tiếp theo.
+- Người phụ trách: Product Designer (UX/UI Designer) phối hợp với Content Strategist.
+- Tài liệu đầu ra: Bản thiết kế giao diện Figma luồng xử lý ngoại lệ (Error Recovery Flow &amp; Wireframe) và Từ điển thông điệp thông báo.
+3. Thay đổi về Kiểm chứng và Giám sát (Verification &amp; QA Change):
+- Nội dung thay đổi: Xây dựng bộ test case kiểm thử tự động gồm 20 câu hỏi ngoài phạm vi (đặt vé tàu, vé xe, khách sạn...) để đảm bảo 100% các câu hỏi này kích hoạt đúng thông điệp từ chối và gợi ý hướng đi mới, không bao giờ xuất hiện lỗi 'đã có lỗi' (500/Internal Error).
+- Người phụ trách: QA Engineer / Evaluation Engineer.
+- Tài liệu đầu ra: Bộ đề kiểm thử hồi quy (Out-of-Scope Test Suite) và Báo cáo kiểm thử tự động (CI/CD Eval Report).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong phát triển sản phẩm AI, một sự cố 'bot báo lỗi khi gặp câu hỏi ngoài phạm vi' không đơn thuần là lỗi kỹ thuật backend, mà phản ánh lỗ hổng trong ba trụ cột: Định nghĩa phạm vi sản phẩm (Product), Thiết kế phản hồi có tính phục hồi (Design), và Bộ kiểm thử hồi quy biên giới (QA). Việc phân chia rõ trách nhiệm và tài liệu đầu ra giúp vòng cải tiến vận hành khép kín.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google PAIR Guidebook - Errors + Failing Gracefully (https://pair.withgoogle.com/guidebook/patterns/errors/)</t>
         </is>
       </c>
     </row>
@@ -933,10 +977,28 @@
       <c r="K10" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Loại các giả định đã có bằng chứng trực tiếp.
-Phân tích theo nguyên lý thiết kế: Loại các giả định đã có bằng chứng trực tiếp.</t>
+- 1.0 điểm: Chọn chính xác Giả định C (tần suất quay lại 3 lần/tuần) là giả định then chốt.
+- 1.0 điểm: Phân loại đúng loại rủi ro của C (Value Risk / User Retention Risk).
+- 1.0 điểm: Lập luận chặt chẽ loại bỏ các giả định A, B, D dựa trên việc đã có bằng chứng thực nghiệm rõ ràng.
+- 1.0 điểm: Đề xuất tín hiệu đo lường tối thiểu cụ thể, có số lượng mẫu, thời gian và tiêu chí định lượng (W2 Retention).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Chọn giả định then chốt (Leap-of-Faith Assumption - LOFA):
+- Giả định được chọn: Giả định C: 'Ứng viên quay lại luyện phỏng vấn ba lần mỗi tuần'.
+2. Phân loại rủi ro và Lý do loại bỏ các giả định khác:
+- Phân loại rủi ro của C: Rủi ro về Giá trị / Sự gắn kết của người dùng (Value &amp; Retention Risk). Đây là rủi ro sống còn quyết định sản phẩm có tạo ra thói quen và duy trì được vòng đời khách hàng hay không. Nếu ứng viên chỉ dùng thử 1 lần rồi bỏ, sản phẩm sẽ thất bại về mặt kinh doanh.
+- Lý do loại các giả định khác:
+  + Giả định A (chấm giọng nói): Đã có bằng chứng kỹ thuật trực tiếp (18/20 tình huống đạt = 90%), rủi ro tính khả thi kỹ thuật (Feasibility) đã được giải tỏa cơ bản.
+  + Giả định B (hiểu phản hồi): Đã được xác thực qua thử nghiệm người dùng (5/5 lượt kiểm tra đạt = 100%), rủi ro khả năng sử dụng (Usability) đã được kiểm chứng sơ bộ.
+  + Giả định D (chịu tải 1.000 user): Đã vượt qua kiểm thử tải (Stress test pass), rủi ro hạ tầng đã có số liệu thực nghiệm.
+  -&gt; Chỉ duy nhất Giả định C là hoàn toàn CHƯA ĐƯỢC ĐO LƯỜNG (Zero evidence) và mang tính quyết định sự tồn tại của sản phẩm.
+3. Đề xuất tín hiệu tối thiểu để kiểm chứng (Minimum Validation Signal):
+- Chạy chương trình thử nghiệm Pilot kéo dài 2 tuần với nhóm mẫu 30 ứng viên mục tiêu.
+- Tín hiệu đo lường: Tỷ lệ người dùng quay lại thực hiện ít nhất 3 phiên phỏng vấn trong tuần thứ hai (W2 Retention Rate &gt;= 3 sessions/week).
+- Tiêu chí đạt: &gt;= 40% người dùng trong nhóm thử nghiệm đạt tần suất này mà không cần nhắc nhở thủ công gượng ép.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Leap-of-Faith Assumption (LOFA) trong Lean Startup và AI Product Management yêu cầu đội ngũ tập trung nguồn lực kiểm chứng giả định có độ bất định cao nhất nhưng lại có tác động sinh tử tới mô hình kinh doanh. Khi các giả định kỹ thuật và giao diện đã có bằng chứng, rủi ro giữ chân người dùng (Retention) chính là giả định then chốt cần thử nghiệm đầu tiên.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Eric Ries - The Lean Startup (Leap of Faith Assumptions) &amp; Marty Cagan - Inspired: How to Create Tech Products Customers Love (https://www.svpg.com/books/inspired-how-to-create-tech-products-customers-love/)</t>
         </is>
       </c>
     </row>
@@ -1017,10 +1079,25 @@
       <c r="K12" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Câu hỏi đang đo quy trình thao tác, không đo độ đẹp hay kỹ thuật phía sau hệ thống.
-Phân tích theo nguyên lý thiết kế: Câu hỏi đang đo quy trình thao tác, không đo độ đẹp hay kỹ thuật phía sau hệ thống.</t>
+- 1.0 điểm: Chọn chính xác mức độ mô phỏng phù hợp (Medium-fidelity clickable prototype / Figma).
+- 1.0 điểm: Mô tả rõ ràng tài liệu cần tạo (luồng 3 màn hình, kịch bản kiểm thử thao tác, bảng quan sát).
+- 1.0 điểm: Liệt kê chi tiết những thứ chưa cần xây dựng (API thật, backend, database, animations, auth).
+- 1.0 điểm: Thể hiện đúng tư duy Lean Product: đo lường nhận thức quy trình, không đo độ đẹp hay công nghệ ngầm.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Lựa chọn mức độ mô phỏng tối thiểu (Minimum Prototype Fidelity):
+- Mức độ lựa chọn: Nguyên mẫu tương tác độ trung thực trung bình (Medium-fidelity Clickable Prototype, ví dụ sử dụng Figma hoặc wireframe tương tác clickable).
+2. Mô tả tài liệu và tài sản cần tạo:
+- Bộ màn hình luồng công việc 3 bước (3-step Flow Screens): Màn hình 1 (Kiểm tra kết quả trích xuất với các trường dữ liệu giả lập), Màn hình 2 (Chỉnh sửa trực tiếp trên ô dữ liệu), Màn hình 3 (Hộp thoại xác nhận cuối cùng trước khi lưu).
+- Kịch bản thử nghiệm khả năng sử dụng (Usability Task Script): Giao cho HR một nhiệm vụ cụ thể: 'Hãy rà soát thông tin ứng viên A, sửa lại năm kinh nghiệm từ 2 thành 3 năm, và xác nhận lưu hồ sơ'.
+- Bảng ghi nhận quan sát: Đo thời gian hoàn thành, các thao tác nhầm lẫn, và câu hỏi 'HR có hiểu vì sao cần bấm xác nhận sau khi sửa hay không?'.
+3. Những thứ TUYỆT ĐỐI CHƯA CẦN XÂY DỰNG ở giai đoạn này:
+- Chưa cần xây dựng hệ thống backend thật hoặc kết nối API OpenAI/LLM thật (dùng dữ liệu mockup tĩnh).
+- Chưa cần hiệu ứng đồ họa phức tạp (animations, transitions), hệ thống thiết kế hoàn chỉnh (Design System) hay chế độ dark mode.
+- Chưa cần cơ sở dữ liệu thật, hệ thống phân quyền đăng nhập hay tối ưu hóa hạ tầng máy chủ.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Mục tiêu của nghiên cứu là kiểm chứng mô hình tâm lý (mental model) của HR về quy trình nghiệp vụ: 'Kiểm tra -&gt; Chỉnh sửa -&gt; Xác nhận'. Để trả lời câu hỏi này, việc đầu tư xây dựng backend thật và hiệu ứng bóng bẩy gây lãng phí lớn nguồn lực kỹ thuật mà không mang lại thêm thông tin hữu ích nào về tính khả dụng của luồng người dùng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Nielsen Norman Group - Prototyping: Low vs. High Fidelity (https://www.nngroup.com/articles/ux-prototype-hi-lo-fidelity/)</t>
         </is>
       </c>
     </row>
@@ -1101,10 +1178,24 @@
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Mô tả đã có toàn bộ luồng; cần hỏi thêm nhóm đang kiểm giá trị của sản phẩm hay thử vận hành gần thực tế.
-Phân tích theo nguyên lý thiết kế: Mô tả đã có toàn bộ luồng; cần hỏi thêm nhóm đang kiểm giá trị của sản phẩm hay thử vận hành gần thực tế.</t>
+- 1.0 điểm: Nêu đúng 2 nhãn tiềm năng là Pilot và MVP (hoặc PoC/Pilot).
+- 1.0 điểm: Chọn chính xác nhãn chính là Pilot kèm lý giải về quy mô 3 cửa hàng, thời hạn 1 tuần và kiểm tra tích hợp thực tế.
+- 1.0 điểm: Nêu rõ điều kiện chuyển thành MVP (mở rộng người dùng tự phục vụ, đo retention/giá trị dài hạn).
+- 1.0 điểm: Phân biệt rõ ràng mục đích kiểm tra giá trị sản phẩm độc lập so với thử nghiệm vận hành có hỗ trợ.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Hai nhãn có thể hợp lý:
+- Nhãn 1: Pilot (Thử nghiệm vận hành thực tế quy mô hẹp).
+- Nhãn 2: MVP (Sản phẩm khả dụng tối thiểu - Minimum Viable Product).
+2. Lựa chọn nhãn chính xác nhất hiện tại:
+- Nhãn chính: PILOT (hoặc Closed Pilot / Field Trial).
+- Lý do: Nhóm đã có luồng hoàn chỉnh từ đầu đến cuối (End-to-End Flow: Nhập -&gt; AI phân loại -&gt; Chủ sửa -&gt; Lưu) và đang triển khai thực tế trên môi trường sản xuất của 3 đối tượng cụ thể trong một khung thời gian giới hạn (1 tuần) nhằm kiểm tra khả năng tích hợp vào thói quen vận hành thực tế của cửa hàng.
+3. Điều kiện khiến nhãn thay đổi:
+- Chuyển sang nhãn MVP: Khi sản phẩm được đóng gói độc lập, mở rộng cho bất kỳ chủ cửa hàng mới nào tự đăng ký và sử dụng (Self-service Onboarding), có mô hình định giá/thương mại hóa hoặc theo dõi chỉ số duy trì (Retention/NPS) dài hạn trên quy mô thị trường mở chứ không còn chịu sự hỗ trợ cầm tay chỉ việc trong 1 tuần của nhóm sáng lập.
+- Chuyển sang nhãn PoC (Proof of Concept): Nếu việc phân loại AI chưa tự động mà chỉ là nhóm dùng một script chạy tay trên máy cá nhân để chứng minh thuật toán có thể phân loại đúng hóa đơn hay không, chưa tạo thành luồng sản phẩm tự vận hành.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Việc phân biệt giữa PoC (chứng minh tính khả thi kỹ thuật), Prototype (kiểm tra tương tác), Pilot (kiểm tra vận hành quy mô nhỏ có thời hạn) và MVP (sản phẩm tối thiểu cung cấp giá trị độc lập trên thị trường) là nền tảng trong quản trị sản phẩm AI. Thử nghiệm với 3 cửa hàng trong 1 tuần mang đầy đủ đặc trưng của một chương trình Pilot vận hành.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Steve Blank &amp; Marty Cagan - Product Management Terminology: PoC, Prototype, Pilot, and MVP (https://www.svpg.com/books/inspired-how-to-create-tech-products-customers-love/)</t>
         </is>
       </c>
     </row>
@@ -1181,10 +1272,26 @@
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Giữ một kết quả rõ ràng; đưa mọi phần không phục vụ kết quả đó ra ngoài phạm vi MVP.
-Phân tích theo nguyên lý thiết kế: Giữ một kết quả rõ ràng; đưa mọi phần không phục vụ kết quả đó ra ngoài phạm vi MVP.</t>
+- 1.0 điểm: Cắt lát phạm vi tập trung duy nhất vào bài toán đi công tác 2 ngày của một người dùng.
+- 1.0 điểm: Mô tả đầy đủ luồng từ đầu đến cuối (E2E) từ lúc nhập thông tin -&gt; AI đề xuất -&gt; duyệt -&gt; nhận lịch trình/hóa đơn.
+- 1.0 điểm: Chọn chính xác 3 tính năng đưa vào backlog từ danh sách (nhà hàng, thời tiết, chia tiền).
+- 1.0 điểm: Giải thích thuyết phục vì sao 3 tính năng này không thuộc luồng giá trị cốt lõi của chuyến công tác.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Cắt lát MVP tối thiểu (End-to-End Slice) cho người dùng đi công tác 2 ngày:
+- Kết quả duy nhất cần đạt được: Đặt thành công phương tiện di chuyển và chỗ ở đáp ứng tiêu chí công tác ngắn ngày.
+- Luồng khép kín từ đầu đến cuối (E2E User Flow):
+  + Bước 1: Người dùng nhập điểm đến, ngày đi và ngày về (2 ngày) kèm chính sách công tác (ví dụ: khách sạn có bàn làm việc, chuyến bay sáng).
+  + Bước 2: AI đề xuất 1 gói hành trình tối ưu duy nhất gồm: 1 chuyến bay khứ hồi phù hợp giờ họp + 1 khách sạn gần địa điểm làm việc.
+  + Bước 3: Người dùng xem xét, điều chỉnh giờ bay/phòng nếu cần, và bấm xác nhận.
+  + Bước 4: Hệ thống thực hiện giữ chỗ/thanh toán và xuất lịch trình chi tiết kèm hóa đơn VAT gửi về email công ty.
+2. Ba tính năng bắt buộc đưa vào danh sách việc để sau (Backlog / Deferred Scope):
+- Tính năng 1: 'Gợi ý nhà hàng' (Nhân viên công tác thường có lịch hẹn với đối tác hoặc tự chọn món nhanh, không mang tính sinh tử cho chuyến đi).
+- Tính năng 2: 'Dự báo thời tiết chi tiết' (Người dùng có thể tự xem app thời tiết mặc định trên điện thoại, không cần thiết kế trong lõi đặt chuyến).
+- Tính năng 3: 'Chia tiền nhóm' (Chuyến đi công tác đơn lẻ 1 người không có nhu cầu chia tiền; đây là tính năng của nhóm du lịch nghỉ dưỡng).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Cắt lát MVP (End-to-End Slicing) đòi hỏi duy trì một lát cắt dọc hoàn chỉnh mang lại giá trị trọn vẹn cho một phân khúc người dùng hẹp (người đi công tác 2 ngày). Bằng cách loại bỏ các tính năng ngoại vi (nhà hàng, thời tiết, chia tiền) sang backlog, đội ngũ giảm được 70% độ phức tạp tích hợp mà vẫn giải quyết triệt để bài toán công tác.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Jeff Patton - User Story Mapping: Discover the Whole Story, Build the Right Product (https://www.jpattonassociates.com/user-story-mapping/)</t>
         </is>
       </c>
     </row>
@@ -1268,10 +1375,29 @@
       <c r="K18" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Nếu chưa có tiêu chí tiếp tục/dừng thì đây mới chỉ là bản minh họa thủ công.
-Phân tích theo nguyên lý thiết kế: Nếu chưa có tiêu chí tiếp tục/dừng thì đây mới chỉ là bản minh họa thủ công.</t>
+- 1.0 điểm: Nêu giả định kiểm chứng rõ ràng về nhu cầu sử dụng và kỳ vọng phân loại của chủ cửa hàng.
+- 1.0 điểm: Mô tả quy trình thao tác thủ công của người phía sau (phù thủy nhập liệu) qua giao diện giả lập AI.
+- 1.0 điểm: Xác định dữ liệu thu thập và thiết lập tiêu chí Tiếp tục / Dừng (Go/No-go criteria) cụ thể.
+- 1.0 điểm: Chỉ ra dứt khoát giới hạn không được khẳng định quá mức (chỉ đo được nhu cầu, chưa chứng minh thuật toán AI tự động).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Thử nghiệm Wizard-of-Oz cho Dịch vụ AI Phân loại Hóa đơn:
+1. Giả định cần kiểm chứng (Core Hypothesis):
+'Các chủ cửa hàng nhỏ sẵn sàng chụp ảnh hóa đơn gửi lên hệ thống và chấp nhận độ trễ trả kết quả trong 15 phút, với điều kiện độ chính xác phân loại danh mục chi phí đạt trên 90% để họ không phải nhập sổ thủ công.'
+2. Thao tác thủ công của 'Phù thủy' (Wizard Operation Behind the Curtain):
+Giao diện phía trước hiển thị như một ứng dụng web AI hiện đại ('Đang tải lên và quét thông minh bằng AI...'). Khi chủ cửa hàng tải ảnh hóa đơn lên, ảnh được chuyển về một kênh Telegram/Slack nội bộ của nhóm sáng lập. Một thành viên trong nhóm đóng vai 'AI' sẽ đọc ảnh, gõ tay các trường (ngày, số tiền, nhà cung cấp, hạng mục chi phí) vào bảng tính và bấm nút gửi trả kết quả về giao diện của chủ cửa hàng trong vòng 10 phút.
+3. Dữ liệu cần thu thập:
+- Số lượng hóa đơn trung bình mỗi chủ cửa hàng tải lên mỗi ngày.
+- Tần suất chủ cửa hàng bấm sửa các hạng mục phân loại.
+- Phản hồi định tính về cảm giác tiện lợi và mức độ tin tưởng đối với kết quả nhận được.
+4. Tiêu chí Tiếp tục / Dừng (Go / No-Go Decision Criteria):
+- TIẾP TỤC (Build Real AI Engine): Nếu &gt;= 70% chủ cửa hàng tham gia thử nghiệm tải hóa đơn liên tục trong 5 ngày và tỷ lệ giữ nguyên nhãn phân loại (không cần sửa) đạt &gt;= 85%.
+- DỪNG / PIVOT: Nếu &lt; 30% chủ cửa hàng tiếp tục tải hóa đơn sau ngày đầu tiên (chứng tỏ rào cản chụp ảnh quá cao hoặc việc phân loại chi phí chưa phải là nỗi đau thực sự).
+5. Giới hạn KHÔNG ĐƯỢC khẳng định quá mức (Experiment Boundary):
+Tuyệt đối không được tuyên bố rằng 'Hệ thống AI đã sẵn sàng hoạt động tự động với chi phí thấp và độ trễ mili-giây'. Kết quả thử nghiệm chỉ chứng minh Nhu cầu của khách hàng đối với dịch vụ phân loại (Value/Demand Validation), hoàn toàn chưa chứng minh tính khả thi kỹ thuật của thuật toán OCR/NLP trong việc tự động hóa hoàn toàn.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Wizard-of-Oz là phương pháp giả lập năng lực tự động hóa bằng con người ở hậu trường để kiểm chứng nhu cầu thị trường trước khi viết code AI. Một thử nghiệm Wizard-of-Oz chuẩn mực bắt buộc phải có tiêu chí Go/No-Go định lượng và phải nhận thức rõ giới hạn: nó chỉ kiểm chứng Value Risk chứ không chứng minh Feasibility Risk.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Alberto Savoia - The Right It: Why So Many Ideas Fail and How to Make Sure Yours Succeed (Pretotyping Techniques) (https://www.pretotyping.org/)</t>
         </is>
       </c>
     </row>
@@ -1352,10 +1478,27 @@
       <c r="K20" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Nếu chỉ hỏi 'có thích không', bạn chưa đo được việc xử lý có nhanh hơn hay không.
-Phân tích theo nguyên lý thiết kế: Nếu chỉ hỏi 'có thích không', bạn chưa đo được việc xử lý có nhanh hơn hay không.</t>
+- 1.0 điểm: Chọn đúng phương pháp kiểm chứng thực nghiệm đối chứng (A/B testing hoặc Time-motion study).
+- 1.0 điểm: Định nghĩa chính xác nhóm đối chứng (gõ tay) và nhóm thử nghiệm (dùng bản nháp AI).
+- 1.0 điểm: Đo lường bằng tín hiệu khách quan (thời gian xử lý trung bình AHT) kết hợp điểm chất lượng.
+- 1.0 điểm: Xác định giới hạn mẫu và tiêu chí ra quyết định (giảm ít nhất 25% thời gian, p &lt; 0.05).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Lựa chọn phương pháp kiểm chứng (Validation Method):
+- Phương pháp: Thử nghiệm A/B Testing có đối chứng ngẫu nhiên (Randomized Controlled Trial - RCT) hoặc Nghiên cứu thử nghiệm định lượng bấm giờ (Time-motion Usability Study).
+2. Định nghĩa tín hiệu đo lường và Nhóm so sánh:
+- Nhóm A (Nhóm đối chứng - Control Group): Nhân viên hỗ trợ xử lý phiếu hỗ trợ theo quy trình thủ công truyền thống (tự gõ câu trả lời từ đầu).
+- Nhóm B (Nhóm can thiệp - Treatment Group): Nhân viên hỗ trợ nhận được bản nháp câu trả lời do AI tạo sẵn và có thể chỉnh sửa trước khi gửi.
+- Tín hiệu đo lường khách quan: Thời gian xử lý trung bình trên mỗi phiếu (Average Handling Time - AHT tính bằng giây) từ lúc mở phiếu đến lúc gửi câu trả lời, kết hợp với Điểm chất lượng phản hồi (Quality/Resolution Score do QA chấm mù).
+3. Giới hạn của mẫu thử (Sample Boundary &amp; Limitations):
+- Thử nghiệm trên 20 nhân viên có kinh nghiệm tương đồng, xử lý cùng một phân loại phiếu có độ khó chuẩn hóa (ví dụ: các phiếu hỏi chính sách hoàn hàng) trong thời gian 2 tuần.
+- Giới hạn: Kết quả chỉ áp dụng cho nhóm phiếu hỗ trợ dạng văn bản có cấu trúc mẫu sẵn; không được suy rộng kết quả cho các phiếu khiếu nại kỹ thuật phức tạp hoặc khủng hoảng truyền thông.
+4. Tiêu chí ra quyết định tối thiểu (Decision Criteria):
+- Chấp nhận triển khai chính thức (Pass): Thời gian xử lý ở Nhóm B giảm ít nhất 25% so với Nhóm A (p-value &lt; 0.05), đồng thời tỷ lệ phiếu đạt chuẩn chất lượng không bị suy giảm (Delta Quality &gt;= 0%).
+- Loại bỏ / Tinh chỉnh lại (Fail): Nếu thời gian chỉnh sửa bản nháp AI khiến tổng thời gian xử lý không giảm hoặc thậm chí tăng lên (do nhân viên mất thời gian sửa câu chữ ngô nghê của AI).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Để chứng minh giả định 'xử lý nhanh hơn', sản phẩm không thể dựa vào các câu hỏi cảm tính ('Bạn có thích AI không?'). Bắt buộc phải sử dụng phương pháp đo lường hành vi khách quan (Time-to-Resolve / Handling Time) trên hai nhóm so sánh đối chứng, với tiêu chí ra quyết định định lượng rõ ràng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Ron Kohavi, Diane Tang, Ya Xu - Trustworthy Online Controlled Experiments: A Practical Guide to A/B Testing (https://experimentguide.com/)</t>
         </is>
       </c>
     </row>
@@ -1434,10 +1577,26 @@
       <c r="K22" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Một khía cạnh thuộc hành vi của đầu ra, khía cạnh còn lại thuộc cách người dùng hiểu đầu ra đó.
-Phân tích theo nguyên lý thiết kế: Một khía cạnh thuộc hành vi của đầu ra, khía cạnh còn lại thuộc cách người dùng hiểu đầu ra đó.</t>
+- 1.0 điểm: Nêu rõ 2 khía cạnh chất lượng riêng biệt: Độ vững chắc của thuật toán (hành vi đầu ra) và Tính minh bạch nhận thức (cách người dùng hiểu).
+- 1.0 điểm: Đưa ra bằng chứng kiểm tra kỹ thuật trên ảnh mờ (đo độ dao động calo).
+- 1.0 điểm: Đưa ra bằng chứng kiểm tra nhận thức người dùng (tránh ngộ nhận con số tuyệt đối).
+- 1.0 điểm: Thiết lập tiêu chí đạt cụ thể: từ chối khi ảnh quá mờ và hiển thị dạng khoảng ước tính (range estimation).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Hai khía cạnh chất lượng cần kiểm soát:
+- Khía cạnh 1: Độ tin cậy và Tính vững chắc của Thuật toán (Algorithmic Robustness &amp; Precision under Degradation).
+  + Bản chất: Năng lực của mô hình nhận diện thực phẩm khi xử lý các đầu vào chất lượng kém (ảnh chụp bị mờ, thiếu sáng, góc chụp khuất).
+- Khía cạnh 2: Tính minh bạch trong Truyền thông và Nhận thức của Người dùng (Transparency &amp; Cognitive Perception of Uncertainty).
+  + Bản chất: Cách giao diện truyền đạt bản chất của con số calo (đây là con số ước tính/khoảng dự báo chứ không phải phép đo chính xác tuyệt đối).
+2. Bằng chứng cần kiểm tra thực tế:
+- Bằng chứng cho Khía cạnh 1: Chạy bộ dữ liệu kiểm thử gồm 100 ảnh mờ ở các mức độ làm mờ (Gaussian blur khác nhau) để đo biên độ dao động của lượng calo dự báo (ví dụ: món phở bị dao động từ 350 kcal đến 700 kcal).
+- Bằng chứng cho Khía cạnh 2: Quan sát người dùng trong thử nghiệm sử dụng (Usability test): Khi thấy kết quả '520 kcal', người dùng có hiểu đây là khoảng dao động hay xem đó là số đo gram tuyệt đối.
+3. Tiêu chí đạt sơ bộ (Preliminary Acceptance Criteria):
+- Tiêu chí thuật toán: Khi phát hiện độ mờ của ảnh vượt ngưỡng an toàn (Blur score &gt; threshold), hệ thống phải từ chối đoán bừa và chủ động yêu cầu: 'Ảnh chụp hơi mờ, bạn vui lòng chụp lại rõ nét hơn'.
+- Tiêu chí giao diện/nhận thức: Không bao giờ hiển thị một con số đơn lẻ tuyệt đối (point estimate). Thay vào đó, hiển thị dạng khoảng ước tính kèm nhãn độ tin cậy: 'Ước tính khoảng 480 – 550 kcal (Độ tin cậy: Trung bình do góc chụp)'.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Chất lượng của một sản phẩm AI bao gồm cả chất lượng kỹ thuật của đầu ra (Output Robustness) và chất lượng giao tiếp về độ bất định tới tâm trí người dùng (User Mental Model Calibration). Việc che giấu sự bất định bằng một con số calo chính xác sẽ tạo ra niềm tin sai lệch (over-reliance) và gây thất vọng lớn khi người dùng phát hiện sai số.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google PAIR Guidebook - Set the Right Expectations &amp; Calibration of Trust in AI Systems (https://pair.withgoogle.com/guidebook/)</t>
         </is>
       </c>
     </row>
